--- a/خلاصه_نتایج.xlsx
+++ b/خلاصه_نتایج.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="خلاصه" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="پرتفوی" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="پرتفوی_سالانه" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="پرتفوی_ماهانه" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مقایسه_سقف_اجرا" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تحلیل_سشن" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="تحلیل_ساعت_خام" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="سشن_هر_نماد" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="پایداری_سشن" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="پرتفوی" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,22 +522,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.08</v>
+        <v>39.19</v>
       </c>
       <c r="C2" t="n">
-        <v>68.92</v>
+        <v>60.81</v>
       </c>
       <c r="D2" t="n">
-        <v>32.52</v>
+        <v>25.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.164</v>
+        <v>0.13</v>
       </c>
       <c r="F2" t="n">
-        <v>14.6</v>
+        <v>17.26</v>
       </c>
       <c r="G2" t="n">
-        <v>1.221</v>
+        <v>1.198</v>
       </c>
       <c r="H2" t="n">
         <v>222</v>
@@ -548,10 +549,10 @@
         <v>17.57</v>
       </c>
       <c r="K2" t="n">
-        <v>394.28</v>
+        <v>367.07</v>
       </c>
       <c r="L2" t="n">
-        <v>32.55</v>
+        <v>25.25</v>
       </c>
       <c r="M2" t="n">
         <v>17.9</v>
@@ -563,7 +564,7 @@
         <v>34</v>
       </c>
       <c r="P2" t="n">
-        <v>-57.92</v>
+        <v>-54.2</v>
       </c>
     </row>
     <row r="3">
@@ -573,22 +574,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.45</v>
+        <v>47.9</v>
       </c>
       <c r="C3" t="n">
-        <v>65.55</v>
+        <v>52.1</v>
       </c>
       <c r="D3" t="n">
-        <v>33.69</v>
+        <v>38.32</v>
       </c>
       <c r="E3" t="n">
-        <v>0.303</v>
+        <v>0.332</v>
       </c>
       <c r="F3" t="n">
-        <v>9.59</v>
+        <v>8.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.431</v>
+        <v>1.596</v>
       </c>
       <c r="H3" t="n">
         <v>119</v>
@@ -600,10 +601,10 @@
         <v>13.45</v>
       </c>
       <c r="K3" t="n">
-        <v>129.42</v>
+        <v>137.4</v>
       </c>
       <c r="L3" t="n">
-        <v>33.71</v>
+        <v>38.36</v>
       </c>
       <c r="M3" t="n">
         <v>13.7</v>
@@ -615,7 +616,7 @@
         <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>-19.4</v>
+        <v>-11.23</v>
       </c>
     </row>
     <row r="4">
@@ -625,37 +626,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.46</v>
+        <v>44.86</v>
       </c>
       <c r="C4" t="n">
-        <v>68.53999999999999</v>
+        <v>55.14</v>
       </c>
       <c r="D4" t="n">
-        <v>39.42</v>
+        <v>54.01</v>
       </c>
       <c r="E4" t="n">
-        <v>0.198</v>
+        <v>0.249</v>
       </c>
       <c r="F4" t="n">
-        <v>12.3</v>
+        <v>10.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1.273</v>
+        <v>1.426</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I4" t="n">
         <v>47</v>
       </c>
       <c r="J4" t="n">
-        <v>22.07</v>
+        <v>21.96</v>
       </c>
       <c r="K4" t="n">
-        <v>581.01</v>
+        <v>652.6900000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>39.47</v>
+        <v>54.15</v>
       </c>
       <c r="M4" t="n">
         <v>22.7</v>
@@ -667,7 +668,7 @@
         <v>38</v>
       </c>
       <c r="P4" t="n">
-        <v>-61.3</v>
+        <v>-49.91</v>
       </c>
     </row>
     <row r="5">
@@ -677,22 +678,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.33</v>
+        <v>41.54</v>
       </c>
       <c r="C5" t="n">
-        <v>66.67</v>
+        <v>58.46</v>
       </c>
       <c r="D5" t="n">
-        <v>42.46</v>
+        <v>33.43</v>
       </c>
       <c r="E5" t="n">
-        <v>0.229</v>
+        <v>0.185</v>
       </c>
       <c r="F5" t="n">
-        <v>12.69</v>
+        <v>10.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.311</v>
+        <v>1.287</v>
       </c>
       <c r="H5" t="n">
         <v>195</v>
@@ -704,10 +705,10 @@
         <v>24.62</v>
       </c>
       <c r="K5" t="n">
-        <v>620.62</v>
+        <v>574.87</v>
       </c>
       <c r="L5" t="n">
-        <v>42.55</v>
+        <v>33.5</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
@@ -719,7 +720,7 @@
         <v>42</v>
       </c>
       <c r="P5" t="n">
-        <v>-65.45999999999999</v>
+        <v>-61.48</v>
       </c>
     </row>
     <row r="6">
@@ -729,22 +730,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.87</v>
+        <v>53.25</v>
       </c>
       <c r="C6" t="n">
-        <v>62.13</v>
+        <v>46.75</v>
       </c>
       <c r="D6" t="n">
-        <v>86.31999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.45</v>
+        <v>0.491</v>
       </c>
       <c r="F6" t="n">
-        <v>8.31</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.684</v>
+        <v>1.995</v>
       </c>
       <c r="H6" t="n">
         <v>169</v>
@@ -756,10 +757,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>209.15</v>
+        <v>230.38</v>
       </c>
       <c r="L6" t="n">
-        <v>86.37</v>
+        <v>99.17</v>
       </c>
       <c r="M6" t="n">
         <v>27.7</v>
@@ -771,7 +772,7 @@
         <v>30</v>
       </c>
       <c r="P6" t="n">
-        <v>-32.27</v>
+        <v>-18.01</v>
       </c>
     </row>
     <row r="7">
@@ -781,22 +782,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.8</v>
+        <v>43.84</v>
       </c>
       <c r="C7" t="n">
-        <v>69.2</v>
+        <v>56.16</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>59.18</v>
       </c>
       <c r="E7" t="n">
-        <v>0.168</v>
+        <v>0.209</v>
       </c>
       <c r="F7" t="n">
-        <v>12.01</v>
+        <v>10.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1.227</v>
+        <v>1.349</v>
       </c>
       <c r="H7" t="n">
         <v>276</v>
@@ -808,10 +809,10 @@
         <v>19.57</v>
       </c>
       <c r="K7" t="n">
-        <v>785.64</v>
+        <v>860.83</v>
       </c>
       <c r="L7" t="n">
-        <v>43.2</v>
+        <v>59.38</v>
       </c>
       <c r="M7" t="n">
         <v>30.4</v>
@@ -823,7 +824,7 @@
         <v>47</v>
       </c>
       <c r="P7" t="n">
-        <v>-70.67</v>
+        <v>-60.31</v>
       </c>
     </row>
     <row r="8">
@@ -833,22 +834,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.53</v>
+        <v>45.32</v>
       </c>
       <c r="C8" t="n">
-        <v>68.47</v>
+        <v>54.68</v>
       </c>
       <c r="D8" t="n">
-        <v>35.17</v>
+        <v>48.11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.188</v>
+        <v>0.238</v>
       </c>
       <c r="F8" t="n">
-        <v>19.31</v>
+        <v>9.33</v>
       </c>
       <c r="G8" t="n">
-        <v>1.257</v>
+        <v>1.405</v>
       </c>
       <c r="H8" t="n">
         <v>203</v>
@@ -860,10 +861,10 @@
         <v>10.34</v>
       </c>
       <c r="K8" t="n">
-        <v>174.16</v>
+        <v>196.77</v>
       </c>
       <c r="L8" t="n">
-        <v>34.94</v>
+        <v>47.95</v>
       </c>
       <c r="M8" t="n">
         <v>29.9</v>
@@ -875,7 +876,7 @@
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>-50.96</v>
+        <v>-39.09</v>
       </c>
     </row>
     <row r="9">
@@ -885,22 +886,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.09</v>
+        <v>45.45</v>
       </c>
       <c r="C9" t="n">
-        <v>65.91</v>
+        <v>54.55</v>
       </c>
       <c r="D9" t="n">
-        <v>26.21</v>
+        <v>26.72</v>
       </c>
       <c r="E9" t="n">
         <v>0.222</v>
       </c>
       <c r="F9" t="n">
-        <v>8.94</v>
+        <v>7.07</v>
       </c>
       <c r="G9" t="n">
-        <v>1.295</v>
+        <v>1.358</v>
       </c>
       <c r="H9" t="n">
         <v>132</v>
@@ -912,10 +913,10 @@
         <v>16.67</v>
       </c>
       <c r="K9" t="n">
-        <v>165.2</v>
+        <v>163.09</v>
       </c>
       <c r="L9" t="n">
-        <v>26.13</v>
+        <v>26.74</v>
       </c>
       <c r="M9" t="n">
         <v>11.6</v>
@@ -927,7 +928,7 @@
         <v>25</v>
       </c>
       <c r="P9" t="n">
-        <v>-45.76</v>
+        <v>-39.53</v>
       </c>
     </row>
     <row r="10">
@@ -937,22 +938,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.25</v>
+        <v>37.04</v>
       </c>
       <c r="C10" t="n">
-        <v>69.75</v>
+        <v>62.96</v>
       </c>
       <c r="D10" t="n">
-        <v>12.73</v>
+        <v>5.86</v>
       </c>
       <c r="E10" t="n">
-        <v>0.101</v>
+        <v>0.052</v>
       </c>
       <c r="F10" t="n">
-        <v>13.97</v>
+        <v>14.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1.131</v>
+        <v>1.074</v>
       </c>
       <c r="H10" t="n">
         <v>162</v>
@@ -964,10 +965,10 @@
         <v>19.75</v>
       </c>
       <c r="K10" t="n">
-        <v>232.13</v>
+        <v>211.84</v>
       </c>
       <c r="L10" t="n">
-        <v>12.75</v>
+        <v>5.87</v>
       </c>
       <c r="M10" t="n">
         <v>10.8</v>
@@ -979,7 +980,7 @@
         <v>26</v>
       </c>
       <c r="P10" t="n">
-        <v>-53.12</v>
+        <v>-50.96</v>
       </c>
     </row>
     <row r="11">
@@ -989,22 +990,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.05</v>
+        <v>41.58</v>
       </c>
       <c r="C11" t="n">
-        <v>68.95</v>
+        <v>58.42</v>
       </c>
       <c r="D11" t="n">
-        <v>25.77</v>
+        <v>26.92</v>
       </c>
       <c r="E11" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="F11" t="n">
-        <v>13.92</v>
+        <v>12.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.209</v>
+        <v>1.25</v>
       </c>
       <c r="H11" t="n">
         <v>190</v>
@@ -1016,10 +1017,10 @@
         <v>21.58</v>
       </c>
       <c r="K11" t="n">
-        <v>401.63</v>
+        <v>387.86</v>
       </c>
       <c r="L11" t="n">
-        <v>25.73</v>
+        <v>27.06</v>
       </c>
       <c r="M11" t="n">
         <v>13.8</v>
@@ -1031,7 +1032,7 @@
         <v>33</v>
       </c>
       <c r="P11" t="n">
-        <v>-58.71</v>
+        <v>-52.14</v>
       </c>
     </row>
     <row r="12">
@@ -1041,22 +1042,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.8</v>
+        <v>41.01</v>
       </c>
       <c r="C12" t="n">
-        <v>68.2</v>
+        <v>58.99</v>
       </c>
       <c r="D12" t="n">
-        <v>35.76</v>
+        <v>31.63</v>
       </c>
       <c r="E12" t="n">
-        <v>0.181</v>
+        <v>0.16</v>
       </c>
       <c r="F12" t="n">
-        <v>14.56</v>
+        <v>10.73</v>
       </c>
       <c r="G12" t="n">
-        <v>1.242</v>
+        <v>1.248</v>
       </c>
       <c r="H12" t="n">
         <v>217</v>
@@ -1068,10 +1069,10 @@
         <v>26.73</v>
       </c>
       <c r="K12" t="n">
-        <v>861.77</v>
+        <v>820.52</v>
       </c>
       <c r="L12" t="n">
-        <v>35.8</v>
+        <v>31.65</v>
       </c>
       <c r="M12" t="n">
         <v>11.4</v>
@@ -1083,7 +1084,7 @@
         <v>38</v>
       </c>
       <c r="P12" t="n">
-        <v>-62.33</v>
+        <v>-57.23</v>
       </c>
     </row>
     <row r="13">
@@ -1093,22 +1094,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.29</v>
+        <v>38.32</v>
       </c>
       <c r="C13" t="n">
-        <v>69.71000000000001</v>
+        <v>61.68</v>
       </c>
       <c r="D13" t="n">
-        <v>44.19</v>
+        <v>35.21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.171</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>19.73</v>
+        <v>15.44</v>
       </c>
       <c r="G13" t="n">
-        <v>1.236</v>
+        <v>1.218</v>
       </c>
       <c r="H13" t="n">
         <v>274</v>
@@ -1120,10 +1121,10 @@
         <v>22.26</v>
       </c>
       <c r="K13" t="n">
-        <v>1027.74</v>
+        <v>944.79</v>
       </c>
       <c r="L13" t="n">
-        <v>44.06</v>
+        <v>35.18</v>
       </c>
       <c r="M13" t="n">
         <v>66.7</v>
@@ -1135,7 +1136,7 @@
         <v>45</v>
       </c>
       <c r="P13" t="n">
-        <v>-68.42</v>
+        <v>-64.28</v>
       </c>
     </row>
     <row r="14">
@@ -1145,25 +1146,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.04</v>
+        <v>42.86</v>
       </c>
       <c r="C14" t="n">
-        <v>67.96000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="D14" t="n">
-        <v>38.1</v>
+        <v>40.31</v>
       </c>
       <c r="E14" t="n">
-        <v>0.203</v>
+        <v>0.206</v>
       </c>
       <c r="F14" t="n">
-        <v>19.73</v>
+        <v>17.26</v>
       </c>
       <c r="G14" t="n">
-        <v>1.281</v>
+        <v>1.349</v>
       </c>
       <c r="H14" t="n">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1185,107 +1186,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تعداد_نماد</t>
+          <t>سشن</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>سقف_پوزیشن_همزمان</t>
+          <t>تعداد</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ریسک_هر_معامله٪</t>
+          <t>درصد_برد</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>معاملات_انجام‌شده</t>
+          <t>میانگین_R</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>معاملات_ردشده_به_خاطر_سقف</t>
+          <t>مجموع_R</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ردشده_سقف_هر_چارت</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ردشده_محدودیت_ضرر</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>درصد_برد</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>فاکتور_سود</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>بازده_خالص٪</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>حداکثر_افت٪</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>اکویتی_نهایی</t>
+          <t>سهم_از_کل_سود٪</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>12</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>لندن</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>569</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>44.82</v>
       </c>
       <c r="D2" t="n">
-        <v>2358</v>
+        <v>0.293</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>166.7</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.06</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="J2" t="n">
-        <v>614.14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="L2" t="n">
-        <v>714137.17</v>
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>همپوشانی لندن-نیویورک</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>567</v>
+      </c>
+      <c r="C3" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>سیدنی/پایان روز</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>222</v>
+      </c>
+      <c r="C4" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="E4" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>آسیا (پایان)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>521</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>آسیا (توکیو)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>341</v>
+      </c>
+      <c r="C6" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="E6" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>نیویورک</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>153</v>
+      </c>
+      <c r="C7" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -1299,76 +1364,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سال</t>
+          <t>ساعت_UTC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>بازده٪</t>
+          <t>تعداد</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>اکویتی_پایان</t>
+          <t>درصد_برد</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>میانگین_R</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>مجموع_R</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>سهم_از_کل_سود٪</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13.12</v>
+        <v>222</v>
       </c>
       <c r="C2" t="n">
-        <v>113118.98</v>
+        <v>45.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>103.86</v>
+        <v>110</v>
       </c>
       <c r="C3" t="n">
-        <v>230604.23</v>
+        <v>37.27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>103.81</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>469987.14</v>
+        <v>22.22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>51.95</v>
+        <v>329</v>
       </c>
       <c r="C5" t="n">
-        <v>714137.17</v>
+        <v>39.82</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>176</v>
+      </c>
+      <c r="C6" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>321</v>
+      </c>
+      <c r="C8" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="E8" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>218</v>
+      </c>
+      <c r="C9" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="E9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" t="n">
+        <v>324</v>
+      </c>
+      <c r="C11" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="n">
+        <v>223</v>
+      </c>
+      <c r="C12" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="E12" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="n">
+        <v>55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.029</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="n">
+        <v>118</v>
+      </c>
+      <c r="C17" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96</v>
+      </c>
+      <c r="C18" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.427</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -1382,492 +1770,590 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ماه</t>
+          <t>نماد</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>بازده٪</t>
+          <t>آسیا (توکیو) (مجموع R)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>اکویتی_پایان</t>
+          <t>آسیا (پایان) (مجموع R)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>سیدنی/پایان روز (مجموع R)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>لندن (مجموع R)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>نیویورک (مجموع R)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>همپوشانی لندن-نیویورک (مجموع R)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>آسیا (توکیو) (تعداد)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>آسیا (پایان) (تعداد)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>سیدنی/پایان روز (تعداد)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>لندن (تعداد)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>نیویورک (تعداد)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>همپوشانی لندن-نیویورک (تعداد)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.12</v>
+        <v>5.1</v>
       </c>
       <c r="C2" t="n">
-        <v>113118.98</v>
+        <v>10.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.61</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>120598.09</v>
+        <v>11.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>27</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.31</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>134232.93</v>
+        <v>9.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>63</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K4" t="n">
+        <v>47</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.14</v>
+        <v>-0.4</v>
       </c>
       <c r="C5" t="n">
-        <v>131366.37</v>
+        <v>-4.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>64</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.85</v>
+        <v>13.3</v>
       </c>
       <c r="C6" t="n">
-        <v>122363.53</v>
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I6" t="n">
+        <v>31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>42</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>GBPJPY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.62</v>
+        <v>11.2</v>
       </c>
       <c r="C7" t="n">
-        <v>125573.29</v>
+        <v>-1.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>38</v>
+      </c>
+      <c r="I7" t="n">
+        <v>67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.48</v>
+        <v>-1.1</v>
       </c>
       <c r="C8" t="n">
-        <v>148781.89</v>
+        <v>5.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>166981.95</v>
+        <v>-1.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>26</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="C10" t="n">
-        <v>169055.08</v>
+        <v>3.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.51</v>
+        <v>1.8</v>
       </c>
       <c r="C11" t="n">
-        <v>168195.97</v>
+        <v>-13.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>46</v>
+      </c>
+      <c r="L11" t="n">
+        <v>19</v>
+      </c>
+      <c r="M11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.2</v>
+        <v>-7.4</v>
       </c>
       <c r="C12" t="n">
-        <v>192079.95</v>
+        <v>22</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>64</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.98</v>
+        <v>-8.5</v>
       </c>
       <c r="C13" t="n">
-        <v>199722.99</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="C14" t="n">
-        <v>230604.23</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="C15" t="n">
-        <v>247495.57</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="C16" t="n">
-        <v>275362.93</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="C17" t="n">
-        <v>290568.77</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="C18" t="n">
-        <v>282263.22</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="C19" t="n">
-        <v>298538.93</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C20" t="n">
-        <v>301434.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="C21" t="n">
-        <v>332880.21</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C22" t="n">
-        <v>333698.79</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="C23" t="n">
-        <v>331127.54</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="C24" t="n">
-        <v>382873.53</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="C25" t="n">
-        <v>424250.1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="C26" t="n">
-        <v>469987.14</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C27" t="n">
-        <v>491107.48</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C28" t="n">
-        <v>489134.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="C29" t="n">
-        <v>513630.21</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="C30" t="n">
-        <v>591043.0600000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="C31" t="n">
-        <v>617997.86</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C32" t="n">
-        <v>618170.49</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C33" t="n">
-        <v>633299.87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="C34" t="n">
-        <v>616646.76</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="C35" t="n">
-        <v>627982.41</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="C36" t="n">
-        <v>688547.51</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="C37" t="n">
-        <v>714137.17</v>
+        <v>7.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>31</v>
+      </c>
+      <c r="I13" t="n">
+        <v>47</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
+      </c>
+      <c r="K13" t="n">
+        <v>101</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1881,103 +2367,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سقف_اجرا</t>
+          <t>سشن</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>تعداد_نماد</t>
+          <t>نیمه۱_تعداد</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>سقف_پوزیشن_همزمان</t>
+          <t>نیمه۱_میانگین_R</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ریسک_هر_معامله٪</t>
+          <t>نیمه۱_مجموع_R</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>معاملات_انجام‌شده</t>
+          <t>نیمه۲_تعداد</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>معاملات_ردشده_به_خاطر_سقف</t>
+          <t>نیمه۲_میانگین_R</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ردشده_سقف_هر_چارت</t>
+          <t>نیمه۲_مجموع_R</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ردشده_محدودیت_ضرر</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>درصد_برد</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>فاکتور_سود</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>بازده_خالص٪</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>حداکثر_افت٪</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>اکویتی_نهایی</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>بدترین_ماه٪</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ماه‌های_منفی</t>
+          <t>نتیجه</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>بدون محدودیت</t>
+          <t>لندن</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>309</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>260</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="G2" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>✅ پایدار (در هر دو نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>آسیا (توکیو)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>179</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="G3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>✅ پایدار (در هر دو نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>همپوشانی لندن-نیویورک</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>281</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>✅ پایدار (در هر دو نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>سیدنی/پایان روز</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>✅ پایدار (در هر دو نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>نیویورک</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>86</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>✅ پایدار (در هر دو نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>آسیا (پایان)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>267</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="D7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>254</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>⚠️ ناپایدار (فقط در یک نیمه سودده)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>تعداد_نماد</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>سقف_پوزیشن_همزمان</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ریسک_هر_معامله٪</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>معاملات_انجام‌شده</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>معاملات_ردشده_به_خاطر_سقف</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ردشده_سقف_هر_چارت</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ردشده_محدودیت_ضرر</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>درصد_برد</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>فاکتور_سود</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>بازده_خالص٪</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>حداکثر_افت٪</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>اکویتی_نهایی</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>12</v>
       </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>2361</v>
       </c>
       <c r="E2" t="n">
-        <v>2372</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1986,224 +2691,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>42.82</v>
       </c>
       <c r="I2" t="n">
-        <v>32.04</v>
+        <v>1.315</v>
       </c>
       <c r="J2" t="n">
-        <v>1.264</v>
+        <v>630.5</v>
       </c>
       <c r="K2" t="n">
-        <v>616.37</v>
+        <v>12.37</v>
       </c>
       <c r="L2" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="M2" t="n">
-        <v>716369.95</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-6.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>هر چارت 2 + سقف 8</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2361</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.261</v>
-      </c>
-      <c r="K3" t="n">
-        <v>603.96</v>
-      </c>
-      <c r="L3" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="M3" t="n">
-        <v>703961.42</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-6.85</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>هر چارت 3 + سقف 10</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2370</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>32.07</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.265</v>
-      </c>
-      <c r="K4" t="n">
-        <v>622.91</v>
-      </c>
-      <c r="L4" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="M4" t="n">
-        <v>722913.72</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-6.85</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>هر چارت 3 + سقف 8</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2370</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>32.07</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.265</v>
-      </c>
-      <c r="K5" t="n">
-        <v>622.91</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="M5" t="n">
-        <v>722913.72</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-6.85</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>هر چارت 1 + سقف 5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2210</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>156</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="K6" t="n">
-        <v>424.81</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="M6" t="n">
-        <v>524808.9399999999</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-7.59</v>
-      </c>
-      <c r="O6" t="n">
-        <v>8</v>
+        <v>730497.39</v>
       </c>
     </row>
   </sheetData>

--- a/خلاصه_نتایج.xlsx
+++ b/خلاصه_نتایج.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\پروژه ها\بکتست پروژه زد\نسخه نهایی\8.3\خروجی\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\پروژه ها\بکتست پروژه زد\نسخه نهایی\9\خروجی\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C1974A-40EE-4F80-A083-DE1D3BEA403C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88948C7B-B14F-4310-A619-743A00DE28FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="خلاصه" sheetId="1" r:id="rId1"/>
@@ -166,16 +166,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,6 +475,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -814,47 +811,49 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
